--- a/output/pdf_financials_xlsx/GENX.xlsx
+++ b/output/pdf_financials_xlsx/GENX.xlsx
@@ -6087,46 +6087,46 @@
         <v>0.034555</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.034555</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.034555</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.034555</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.055519</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.055519</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.055519</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.055519</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.055519</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.01273</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.01273</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.01273</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.040087</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.080086</v>
       </c>
     </row>
     <row r="93">
@@ -10304,7 +10304,11 @@
           <t>Warrants reserve 9</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -11547,7 +11551,11 @@
           <t>Warrants reserve 10</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -12426,7 +12434,11 @@
           <t>Warrants reserve 12</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -14349,7 +14361,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -15347,7 +15363,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -27808,7 +27828,7 @@
         <v>-0.193371</v>
       </c>
       <c r="K191" s="5" t="n">
-        <v>0.031667</v>
+        <v>-0.031667</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GENX.xlsx
+++ b/output/pdf_financials_xlsx/GENX.xlsx
@@ -1127,19 +1127,19 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.001452</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.000148</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.000354</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.000178</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.000222</v>
       </c>
     </row>
     <row r="13">
@@ -2203,19 +2203,19 @@
         <v>-0.164701</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.652516</v>
+        <v>-1.653968</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.073998</v>
+        <v>-1.074146</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-4.395574</v>
+        <v>-4.395928</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.073196</v>
+        <v>-0.07337399999999999</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.335055</v>
+        <v>-0.335277</v>
       </c>
     </row>
     <row r="28">
@@ -2331,19 +2331,19 @@
         <v>-0.164701</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.639164</v>
+        <v>-1.640616</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.05343</v>
+        <v>-1.053578</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-4.391842</v>
+        <v>-4.392196</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.073196</v>
+        <v>-0.07337399999999999</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.335055</v>
+        <v>-0.335277</v>
       </c>
     </row>
     <row r="30">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-35570.11419778084</v>
+        <v>-35572.98129100186</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-1806.862503085658</v>
+        <v>-1811.256479881511</v>
       </c>
       <c r="R30" s="1" t="inlineStr">
         <is>
@@ -2564,55 +2564,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.177003</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.179262</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.027601</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.075562</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.583147</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.33855</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.361981</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.270014</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.111536</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.101058</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.069897</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.031347</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.138813</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.009266999999999999</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.011631</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.01148</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.043588</v>
       </c>
     </row>
     <row r="35">
@@ -2680,55 +2680,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.177003</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.179262</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.027601</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.075562</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.583147</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.33855</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.361981</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.270014</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.111536</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.101058</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.069897</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.031347</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.138813</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.009266999999999999</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.011631</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.01148</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.043588</v>
       </c>
     </row>
     <row r="37">
@@ -3376,55 +3376,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.182484</v>
+        <v>0.005481</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.180462</v>
+        <v>0.0012</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.045338</v>
+        <v>0.017737</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.075562</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.645363</v>
+        <v>0.062216</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.418014</v>
+        <v>0.07946400000000001</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.377421</v>
+        <v>0.01544</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.270014</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.111536</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.101058</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.084455</v>
+        <v>0.014558</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.036347</v>
+        <v>0.005</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.1785</v>
+        <v>0.039687</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.052497</v>
+        <v>0.04323</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.055034</v>
+        <v>0.043403</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.032993</v>
+        <v>0.021513</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.049238</v>
+        <v>0.00565</v>
       </c>
     </row>
     <row r="49">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -18513,7 +18513,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
@@ -33722,7 +33722,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -34120,7 +34120,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -35607,7 +35607,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -37829,7 +37829,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -38534,7 +38534,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
